--- a/artfynd/S 2968-2025 artfynd.xlsx
+++ b/artfynd/S 2968-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273034</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273036</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273037</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273038</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,6 +1247,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273039</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1332,6 +1362,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273043</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1442,6 +1477,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273046</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1552,6 +1592,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273047</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1662,6 +1707,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273062</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1772,6 +1822,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273077</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1882,6 +1937,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273090</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1992,6 +2052,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273130</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2102,6 +2167,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273131</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2212,6 +2282,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273139</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2322,6 +2397,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273550</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2432,6 +2512,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273851</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2542,6 +2627,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273865</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2652,6 +2742,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273868</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2762,6 +2857,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273869</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2872,6 +2972,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273870</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2982,6 +3087,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273871</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3092,6 +3202,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273873</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3202,6 +3317,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273875</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3312,6 +3432,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273876</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3422,8 +3547,40 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273877</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>